--- a/output/pdf_financials_xlsx/GBT.xlsx
+++ b/output/pdf_financials_xlsx/GBT.xlsx
@@ -2133,40 +2133,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.495</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.743</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.485</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.872</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.601</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.792</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.983</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.501</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="35">
@@ -2219,40 +2219,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.495</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.743</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.485</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.872</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.601</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.792</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.983</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.501</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="37">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.139</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2750,10 +2750,10 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.167</v>
+        <v>0.155</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -2762,13 +2762,13 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.321</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="49">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -17454,7 +17454,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -20932,7 +20932,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -22544,7 +22544,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E204" s="5" t="n">

--- a/output/pdf_financials_xlsx/GBT.xlsx
+++ b/output/pdf_financials_xlsx/GBT.xlsx
@@ -5633,13 +5633,13 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.547</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="K112" s="1" t="inlineStr">
         <is>
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.478</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="113">
@@ -24980,7 +24980,11 @@
           <t>Proceeds from disposal of property, plant and equipment 9 251</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -28166,7 +28170,11 @@
           <t>Proceeds from disposal property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -34680,7 +34688,11 @@
           <t>Proceeds from disposal of property, plant and equipment 845</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -36102,7 +36114,11 @@
           <t>Proceeds from disposal of property, plant and equipment 2</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E386" s="5" t="n">
         <v>0.09</v>
       </c>

--- a/output/pdf_financials_xlsx/GBT.xlsx
+++ b/output/pdf_financials_xlsx/GBT.xlsx
@@ -1230,20 +1230,14 @@
       <c r="D17" s="3" t="n">
         <v>-0.056</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="3" t="n">
+        <v>-0.788</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-0.005</v>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
@@ -5888,7 +5882,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
     </row>
     <row r="117">
@@ -24904,7 +24898,11 @@
           <t>Purchase of intangible assets 11 (4</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -43082,7 +43080,11 @@
           <t>Income tax recovery (expense) 4 17 635</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
@@ -44388,7 +44390,11 @@
           <t>Income tax recovery (expense) (5 010)</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
           <t>-</t>
